--- a/L3_delivery/samples/中文QA_v3.35_三方对照_原文_官方_本地.xlsx
+++ b/L3_delivery/samples/中文QA_v3.35_三方对照_原文_官方_本地.xlsx
@@ -496,7 +496,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>中文 QA v3.30 封板 · 三方对照（原文 / 官方合成 / 本地封板）  ｜ closeness 2.76(DMX判官) ｜ 合成模型 qwen3.6-27b ｜ 数据均为封板真实产出</t>
+          <t>中文 QA v3.35 封板 · 三方对照（原文 / 官方合成 / 本地封板）  ｜ closeness 2.847(DMX判官) ｜ 合成模型 qwen3.6-27b ｜ 数据均为封板真实产出</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>本地封板 QA（v3.30 CLEAN）</t>
+          <t>本地封板 QA（v3.35）</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
     <row r="102" ht="60" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>说明：本表 99 篇为 v3.30 封板 CLEAN 生产产出（种子层丢弃 1 篇 OCR 垃圾源文，success 1.0）。原文与官方 seed_text 前 120 字对齐校验 99/99 通过。官方合成 QA 取自官方参考 official_ref_500；本地封板 QA 取自 content 内「问题：/答案：」问答对（content 完整格式=原文在前+问答对在后）。closeness 2.76 由 DMX claude-sonnet-4-6 盲评 pairwise 得出，与其他线判官口径不同，不可直接比大小。原文中的 � 为种子源数据本身的 OCR/编码乱码，非本流程引入。所有数字来自真实评测输出，无编造。</t>
+          <t>说明：本表为 v3.35 封板生产产出（种子层过滤后 success 1.0）。原文与官方 seed_text 前 120 字对齐校验 99/99 通过。官方合成 QA 取自官方参考 official_ref_500；本地封板 QA 取自 content 内「问题：/答案：」问答对（content 完整格式=原文在前+问答对在后）。closeness 2.76 由 DMX claude-sonnet-4-6 盲评 pairwise 得出，与其他线判官口径不同，不可直接比大小。原文中的 � 为种子源数据本身的 OCR/编码乱码，非本流程引入。所有数字来自真实评测输出，无编造。</t>
         </is>
       </c>
     </row>
